--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-03T08:42:19+00:00</t>
+    <t>2026-07-09T18:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T18:12:06+00:00</t>
+    <t>2026-07-09T18:19:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T18:19:16+00:00</t>
+    <t>2026-07-15T06:27:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T06:27:44+00:00</t>
+    <t>2026-07-15T13:41:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T13:41:49+00:00</t>
+    <t>2026-07-15T16:11:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T16:11:54+00:00</t>
+    <t>2026-07-16T08:21:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T08:21:58+00:00</t>
+    <t>2026-07-16T08:46:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T08:46:36+00:00</t>
+    <t>2026-07-16T10:52:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T10:52:32+00:00</t>
+    <t>2026-07-16T11:12:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T11:12:17+00:00</t>
+    <t>2026-07-16T21:31:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T21:31:30+00:00</t>
+    <t>2026-07-17T08:00:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T08:00:04+00:00</t>
+    <t>2026-07-17T11:25:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T11:25:46+00:00</t>
+    <t>2026-07-17T14:49:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T14:49:58+00:00</t>
+    <t>2026-07-19T17:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-19T17:20:25+00:00</t>
+    <t>2026-07-21T08:40:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:40:48+00:00</t>
+    <t>2026-07-21T15:50:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T15:50:20+00:00</t>
+    <t>2026-07-21T16:28:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:28:50+00:00</t>
+    <t>2026-07-21T16:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:53:48+00:00</t>
+    <t>2026-07-22T08:07:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T08:07:11+00:00</t>
+    <t>2026-07-22T10:39:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T10:39:39+00:00</t>
+    <t>2026-07-22T17:16:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -266,7 +266,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/pdlgc/ValueSet/pdlgc-repo-type-vs|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/pdlgc/ValueSet/vs-pdlgc-archive-type|0.1.0</t>
   </si>
   <si>
     <t>pdlgc-manifest-archives.nom</t>
@@ -628,7 +628,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.44921875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="63.6796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest-archives.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T17:16:50+00:00</t>
+    <t>2026-07-23T08:53:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
